--- a/data/numeric/input/data_203/7-10DST.xlsx
+++ b/data/numeric/input/data_203/7-10DST.xlsx
@@ -44812,18 +44812,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0665F58-5720-464E-81D3-B33C02B14106}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995EC6BB-BC08-46D7-A42A-83F3DDE42ADE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{464A31FE-E8BE-469C-9969-6BB92CDBE176}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{983A2C80-F922-438A-A89E-15DC881DFBB9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49A5CC9B-768E-4764-8FC2-2676FB644202}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C812DA1C-C24C-4AAB-A53F-E081479814D1}"/>
 </file>